--- a/光伏配储项目/电价数据/2026/赤坎站.xlsx
+++ b/光伏配储项目/电价数据/2026/赤坎站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50989</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.72151</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56474</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5169600000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.45391</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44856</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43786</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45467</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26803</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.21501</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.25887</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07726999999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06342</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.0518</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.03240999999999999</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04498</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.008880000000000001</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.01677</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08623</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.01573</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.00109</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00356</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14524</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21299</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23616</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.2141</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.11595</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.00404</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00688</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.15639</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.02396</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.19147</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22351</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.03614</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.00774</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.12306</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.19467</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.26592</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.00524</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.23596</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.00294</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.45559</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.48512</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.76488</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6153099999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.5134500000000001</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.5141</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.14347</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.58954</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5433600000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.27418</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.50196</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.50482</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.61697</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.5732999999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.42956</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40166</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.33371</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.62495</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.43174</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7574</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.12895</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.20316</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52773</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50769</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51609</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.5115299999999999</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39514</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47737</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37244</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42544</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.52858</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.65547</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.75291</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44291</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.14141</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44885</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.08968999999999999</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.30307</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.04456</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.26416</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.20523</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.11453</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.26709</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.25786</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.5917899999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.22353</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.2746499999999999</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.27321</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.5850700000000001</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.39278</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.01668</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.26557</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.26609</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.23197</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.16021</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.23445</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.26137</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.22939</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.27315</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.44013</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.27033</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.47726</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.29057</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.70962</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.18944</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.51391</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.27577</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.84796</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.82888</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43836</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.59876</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43915</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43385</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40792</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3094</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.2719</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.47407</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.29237</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.29167</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.28471</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.28676</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44852</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.2247</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.20038</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.19161</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.01503</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.06254999999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.03802000000000001</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.14428</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.07962000000000001</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.04040999999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.19079</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.27825</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.07190000000000001</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.21802</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.15024</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.20818</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.19532</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24863</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.24535</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.28712</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27976</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.23832</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.25106</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.22061</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.0608</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.29682</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.4811</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.00395</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.50248</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.29187</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.29086</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39549</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34411</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.27019</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.27374</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47912</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.27374</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.28121</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.28312</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.27984</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.2804700000000001</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.26155</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26396</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.19434</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.10827</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11231</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08176</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.25017</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.21194</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.13234</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28857</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.4494</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.21478</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.04292</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.0439</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06116</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.27075</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.17575</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.04244</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.00766</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.21281</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.00022</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.03171</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.07747</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.20104</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.1658</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.20295</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.15101</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.19519</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14189</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.19927</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.22691</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.2789700000000001</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.25793</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28755</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.46971</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.25512</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.2911</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29226</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29219</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.27536</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.27368</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.27642</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26046</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04074000000000001</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04514</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04027</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04002</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04268</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04552</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04649</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04713000000000001</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04796</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04645000000000001</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04679999999999999</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04764</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04685</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04586999999999999</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04802</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04991</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.0465</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04799</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.0492</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04879</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04647999999999999</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04731</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22001</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04643</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04885</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05164</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00212</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.1471</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03759000000000001</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09887</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39542</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41228</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4173</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35132</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66443</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44655</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42373</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10243</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04263</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04589</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04508</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.0418</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03236</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04065999999999999</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10695</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00109</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.0374</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04688000000000001</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04107</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04124</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04116</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04373</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04366</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04354</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04105</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04046</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04326</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04031000000000001</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03895000000000001</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04342</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.0437</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04106</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04214</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.03996</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04264</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04303</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04643</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20237</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14483</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29974</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29343</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27142</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33777</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32298</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29058</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28381</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27355</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.2737</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28342</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17438</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.16065</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17327</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14961</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16133</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.16072</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23964</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21614</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22874</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27202</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28859</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29316</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28381</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28346</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28336</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28322</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.27262</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>-0.03757</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.26964</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.29604</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.06833</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.28814</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.28701</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.28712</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15729</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.1842</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.28739</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.28723</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50751</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79108</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6219199999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78086</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92003</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4943</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92816</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.9071699999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31965</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.9302999999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63886</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.22914</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88962</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.58099</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.37397</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.06252</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5740499999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.82773</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.8099400000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.80684</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8813200000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8931699999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.52767</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.43238</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.44421</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.48935</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.25132</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8800800000000001</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5517799999999999</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.66583</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54927</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.51034</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46121</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42945</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44492</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45204</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45326</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39689</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43438</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41382</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45134</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58972</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42855</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5968600000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60201</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.64458</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45482</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44742</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.86514</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.23497</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.64637</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.6304999999999999</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.76875</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.22911</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43428</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>-0.04904</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27336</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45282</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35329</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.02615</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.49984</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.50298</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.62197</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.69653</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41538</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4099100000000001</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.45072</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.51264</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.44906</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50063</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28077</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16474</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28521</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26109</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.2012</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27747</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>-0.02041</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27596</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.27242</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.25465</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.24879</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27493</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.24494</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59766</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8897699999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35769</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13647</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7119099999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8059700000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65126</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45101</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45033</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50042</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43988</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42367</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5009</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43409</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42832</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43442</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39603</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.26532</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.26538</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.27149</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.2784</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.26961</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.25609</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.25202</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.24799</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.25575</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.03124</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.20928</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.26722</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.24566</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24997</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.008019999999999999</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.10082</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.23852</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28507</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.02114</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.14303</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.27751</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.06883</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.24565</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26865</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.24479</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.27618</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.29447</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.48784</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.43205</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.60819</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46576</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.68383</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46675</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43963</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42564</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3882</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32656</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42576</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40228</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.00959</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.29466</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.01686</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23723</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14655</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14925</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.1562</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14481</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14239</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14487</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.1438</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26885</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14338</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05349</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11481</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11374</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14764</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14257</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14782</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28879</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.27693</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38275</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38617</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45144</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40367</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43774</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44183</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44128</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44622</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44548</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39906</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35071</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.43604</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47036</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42545</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38262</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39466</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.29051</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>-0.01886</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>-0.02498</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.24541</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.24564</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.23792</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>-0.03838</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.17664</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.08606999999999999</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>-0.04125</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.14134</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>-0.03411</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>-0.03681</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.19346</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.17228</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>-0.03286</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.19121</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.20162</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>-0.0415</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.17401</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.0335</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.20596</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>-0.04022999999999999</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.20304</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>-0.04063</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>-0.01276</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.28311</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44719</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.4602</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24952</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.42663</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41771</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.5138400000000001</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36064</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39232</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28473</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.25754</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.23444</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.27498</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.25009</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.27007</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.27496</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03294</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25471</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24999</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.21058</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07514</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18462</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24501</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28647</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.27129</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25335</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29829</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27477</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42859</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.50648</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41658</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.77843</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.45161</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46938</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.43742</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41745</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31032</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.28233</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.28486</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.28498</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28265</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28771</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.28797</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34354</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.73841</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.41635</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36708</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38266</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42955</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40731</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64954</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.87764</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48756</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.48749</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46045</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34508</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41167</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26149</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13635</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28417</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28271</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19533</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.2465</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27858</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.02818</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.13084</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.01938</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28408</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23774</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28744</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24809</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.00659</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.1451</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.0216</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.23457</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.23727</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29813</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41764</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.3682</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40887</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6379</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60673</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5849500000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46227</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.5876399999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47812</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.73811</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45408</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46009</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40226</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48187</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43061</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41998</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3602</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49346</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.47504</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4669</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.45788</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42157</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40751</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41142</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41981</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41405</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41153</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41906</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45083</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45002</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56137</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50096</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45098</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.41649</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41986</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37515</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42726</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.40545</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29411</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.27274</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.27175</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.16691</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>-0.01777</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.15371</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.04219</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.03461</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.15867</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.17547</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.02261</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.10778</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.009259999999999999</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.26976</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.03691</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41556</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48613</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50844</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.42873</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.5814900000000001</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.6691900000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.6534500000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.63017</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.6951000000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.51493</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5024999999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.76425</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7075199999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.57598</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.61934</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.40659</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.41323</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.46744</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.46419</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.45765</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41204</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5142599999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.43401</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.44767</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4289</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41972</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44424</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41193</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39684</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44857</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39557</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40273</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39528</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38133</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36759</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39468</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29629</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15869</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.27386</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03866</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40843</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45283</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40813</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46381</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01499</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29086</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.39475</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39511</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39456</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37565</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36271</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44381</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.29606</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.29642</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.23501</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.18481</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.2623</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24914</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23555</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23729</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24654</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25207</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.04021</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.03255</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.14074</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.05743</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.17628</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25951</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.04055</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14869</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15242</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.05937</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.01044</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.11431</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.03009</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.13901</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.03768</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.01162</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36733</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35129</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.19218</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.18746</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.13091</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.14954</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.04797999999999999</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01618</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00148</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.04366</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04146</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.13844</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.19067</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27693</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.22293</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.22356</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.22441</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.22866</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.23894</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.26583</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.24859</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.24186</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.23313</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.24902</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25267</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.23549</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.25388</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.24251</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.25994</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.24782</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.26102</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.27543</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.27545</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.25812</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.21738</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.23788</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.21567</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.08302</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.03975</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.23624</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.04663</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.15434</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.15684</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.15722</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.02173</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.23317</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.21834</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.20066</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16469</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15884</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.13148</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.15836</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.18786</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.10849</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.12513</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.19056</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.15918</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.21006</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.18238</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.1705</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.22333</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.16961</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.22065</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.22791</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.20978</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.21704</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.13019</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.44244</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.19438</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>-0.00078</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.17062</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.16697</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04718</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.02522</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.18667</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.26593</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.08053</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.04851</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.01205</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.04893</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23509</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28085</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25289</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.28246</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.20067</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32628</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.10567</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.27529</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.26064</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25482</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.12088</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24451</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39737</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.28883</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.29353</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>-0.01298</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25684</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26983</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.18969</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14341</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.10605</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33217</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.24049</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.26351</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.27686</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.22313</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>-0.0438</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.24722</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.25711</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.29641</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.27436</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28405</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.26782</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.17639</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.26189</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.26532</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.26721</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26332</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.24836</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28293</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30821</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.28226</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>-0.00382</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.00058</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.27621</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42208</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.2755</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.29958</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.52337</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.01121</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.27634</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40558</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.5486799999999999</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.47856</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.45606</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.43135</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.8757699999999999</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.50036</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.42885</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.44926</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40301</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39051</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.38566</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36903</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46778</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.29752</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.29096</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.46409</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.21007</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.17784</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23523</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.27531</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.28682</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2767</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.26198</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.19367</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.26663</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.27724</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.29318</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.29892</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.28176</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41501</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39497</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.4664700000000001</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.56055</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.52565</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46223</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.55201</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46541</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49801</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.53318</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.52088</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7603</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.8038999999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.55049</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55316</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44497</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39139</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37688</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27246</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.29053</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.29549</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.29822</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.2711</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.26778</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.27935</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.26666</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.26235</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.25477</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.24791</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.23669</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.25377</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.18987</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.21191</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.13529</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.00362</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.03894</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>-0.00954</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01295</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.13098</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01156</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02282</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.02345</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23549</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.01516</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02176</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03129</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.0221</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.01574</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01835</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.10451</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.06470999999999999</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11911</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.13838</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.16605</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.22299</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18122</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.18686</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.20751</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.2496</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36664</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38622</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40519</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41917</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38081</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.74113</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38413</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37312</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.30513</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.28373</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.27574</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.27101</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.26103</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.23249</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22627</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.19535</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.19533</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.19976</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.21546</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>-0.02186</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>-0.01621</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>-0.01832</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.01891</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03611</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.07761</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>-0.04076</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.004690000000000001</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01401</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04425</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.009779999999999999</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.01024</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.00381</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15532</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.01876</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.02314</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>-0.01954</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>-0.00363</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>-0.02748</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>-0.02623</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>-0.03706</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.05057</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.22626</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.18164</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.23309</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.26904</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43137</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38182</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5282</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38449</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39783</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40865</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43154</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38499</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.38603</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38726</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5122100000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39567</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41718</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.23126</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.17109</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.11216</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.14717</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.17346</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.16073</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.08654000000000001</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04762</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.06931</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03661</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03739</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03808</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03689</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04518</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05117</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.05952</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.0344</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.05635</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.07122000000000001</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.11358</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.14022</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.08579000000000001</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.16179</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.14334</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.08853</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04601</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21392</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.09469</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.09048</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.18616</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.12907</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.13997</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.16512</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.14527</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.17992</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.1988</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.19984</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.21261</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.25444</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.25834</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.25987</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40437</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.27256</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38804</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.41352</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49799</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.41023</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41841</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44354</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41532</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.41576</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41484</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38213</v>
       </c>
     </row>
   </sheetData>
